--- a/data/trans_dic/P1410-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1410-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 11,93</t>
+          <t>8,36; 11,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 11,9</t>
+          <t>8,07; 12,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,71</t>
+          <t>6,0; 9,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 16,0</t>
+          <t>10,5; 15,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,54</t>
+          <t>6,57; 9,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 10,82</t>
+          <t>7,75; 10,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 12,63</t>
+          <t>8,4; 12,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,79; 14,16</t>
+          <t>10,76; 14,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,01</t>
+          <t>7,69; 10,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,71</t>
+          <t>8,24; 10,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,72</t>
+          <t>7,89; 10,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 14,25</t>
+          <t>11,04; 13,96</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,6</t>
+          <t>1,37; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,4</t>
+          <t>1,14; 2,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,69</t>
+          <t>2,15; 3,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,56</t>
+          <t>3,1; 4,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,95</t>
+          <t>0,82; 1,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,08</t>
+          <t>0,88; 2,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,08</t>
+          <t>1,76; 3,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,35</t>
+          <t>1,62; 2,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,09</t>
+          <t>1,24; 2,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,98</t>
+          <t>1,17; 2,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,17</t>
+          <t>2,14; 3,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,19</t>
+          <t>2,5; 3,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,47</t>
+          <t>1,55; 4,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,71</t>
+          <t>0,2; 1,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,36</t>
+          <t>0,78; 3,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,7</t>
+          <t>3,2; 5,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,38</t>
+          <t>0,96; 3,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,51</t>
+          <t>1,57; 3,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,68</t>
+          <t>1,0; 2,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,3</t>
+          <t>0,21; 1,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,81</t>
+          <t>1,1; 2,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,2</t>
+          <t>2,61; 4,33</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,34</t>
+          <t>3,91; 5,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,57</t>
+          <t>3,26; 4,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,48</t>
+          <t>3,21; 4,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 5,94</t>
+          <t>4,77; 6,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,46</t>
+          <t>3,15; 4,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,87</t>
+          <t>3,54; 4,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,27</t>
+          <t>3,8; 5,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,7</t>
+          <t>3,86; 4,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,66</t>
+          <t>3,71; 4,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,52</t>
+          <t>3,61; 4,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,69</t>
+          <t>3,71; 4,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,09</t>
+          <t>4,38; 5,3</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68717</t>
+          <t>73867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92648</t>
+          <t>100466</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>161365</t>
+          <t>174333</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85759; 123113</t>
+          <t>86214; 122641</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78648; 115965</t>
+          <t>78644; 118548</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44437; 73216</t>
+          <t>45273; 72267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56425; 82221</t>
+          <t>60669; 89128</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>85329; 125420</t>
+          <t>86439; 126206</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>103173; 144647</t>
+          <t>103527; 146181</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85054; 125619</t>
+          <t>83587; 125678</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81194; 106532</t>
+          <t>88276; 116114</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>181945; 235003</t>
+          <t>180482; 235775</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>188458; 247504</t>
+          <t>190358; 249925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136072; 187571</t>
+          <t>137947; 185172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>144444; 180428</t>
+          <t>154395; 195139</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81159</t>
+          <t>85237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>45051</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>120303</t>
+          <t>130288</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22416; 43997</t>
+          <t>23260; 44690</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22510; 47195</t>
+          <t>22362; 46214</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46105; 76680</t>
+          <t>44553; 76795</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56972; 104275</t>
+          <t>69124; 104401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12966; 30967</t>
+          <t>13006; 30073</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15076; 36452</t>
+          <t>15434; 37162</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32423; 61203</t>
+          <t>35015; 60916</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26732; 52563</t>
+          <t>35032; 59362</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39684; 68431</t>
+          <t>40544; 67512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43472; 73489</t>
+          <t>43569; 74810</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85707; 128908</t>
+          <t>86947; 128424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93212; 144250</t>
+          <t>109962; 152849</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>31274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42311</t>
+          <t>48785</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8355; 24625</t>
+          <t>8545; 23843</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>981; 8208</t>
+          <t>979; 8032</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4029; 18398</t>
+          <t>4249; 19235</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19433; 36840</t>
+          <t>22749; 42349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 8320</t>
+          <t>0; 8110</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7337</t>
+          <t>0; 6656</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5020; 18544</t>
+          <t>5287; 18872</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10539; 23183</t>
+          <t>11507; 25363</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10294; 27532</t>
+          <t>10249; 27172</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1976; 12251</t>
+          <t>1992; 11728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12346; 30777</t>
+          <t>12088; 31159</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32508; 54878</t>
+          <t>37701; 62568</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176383</t>
+          <t>190378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>323978</t>
+          <t>353406</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>128507; 175060</t>
+          <t>128162; 176137</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>111617; 156188</t>
+          <t>111479; 157585</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106648; 151465</t>
+          <t>108354; 151800</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>132531; 204945</t>
+          <t>167754; 217750</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>105205; 150696</t>
+          <t>106550; 149062</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>126154; 172797</t>
+          <t>125697; 173111</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>135225; 186273</t>
+          <t>134189; 186910</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>120522; 171597</t>
+          <t>143583; 183381</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>244433; 310370</t>
+          <t>246647; 309740</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>248992; 315234</t>
+          <t>251815; 316202</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>253792; 323747</t>
+          <t>256022; 323305</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>279049; 361015</t>
+          <t>317233; 384108</t>
         </is>
       </c>
     </row>
